--- a/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -728,25 +728,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>14700</v>
+        <v>15100</v>
       </c>
       <c r="E8" s="3">
-        <v>14900</v>
+        <v>15300</v>
       </c>
       <c r="F8" s="3">
-        <v>15000</v>
+        <v>15400</v>
       </c>
       <c r="G8" s="3">
-        <v>14700</v>
+        <v>15100</v>
       </c>
       <c r="H8" s="3">
-        <v>15200</v>
+        <v>15600</v>
       </c>
       <c r="I8" s="3">
-        <v>14000</v>
+        <v>14300</v>
       </c>
       <c r="J8" s="3">
-        <v>15100</v>
+        <v>15400</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -772,22 +772,22 @@
         <v>2200</v>
       </c>
       <c r="E9" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="F9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H9" s="3">
         <v>2700</v>
       </c>
-      <c r="G9" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2600</v>
-      </c>
       <c r="I9" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="J9" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -810,25 +810,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F10" s="3">
         <v>12600</v>
       </c>
-      <c r="E10" s="3">
-        <v>13300</v>
-      </c>
-      <c r="F10" s="3">
-        <v>12300</v>
-      </c>
       <c r="G10" s="3">
-        <v>12300</v>
+        <v>12600</v>
       </c>
       <c r="H10" s="3">
-        <v>12600</v>
+        <v>12900</v>
       </c>
       <c r="I10" s="3">
-        <v>12000</v>
+        <v>12200</v>
       </c>
       <c r="J10" s="3">
-        <v>12500</v>
+        <v>12800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -868,25 +868,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="G12" s="3">
+        <v>8500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I12" s="3">
         <v>7900</v>
       </c>
-      <c r="E12" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>7400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>8300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>7700</v>
-      </c>
       <c r="J12" s="3">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -1046,25 +1046,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17400</v>
+        <v>17900</v>
       </c>
       <c r="E17" s="3">
-        <v>16100</v>
+        <v>16500</v>
       </c>
       <c r="F17" s="3">
-        <v>20600</v>
+        <v>21100</v>
       </c>
       <c r="G17" s="3">
-        <v>21400</v>
+        <v>22000</v>
       </c>
       <c r="H17" s="3">
-        <v>19900</v>
+        <v>20400</v>
       </c>
       <c r="I17" s="3">
-        <v>18600</v>
+        <v>19100</v>
       </c>
       <c r="J17" s="3">
-        <v>16300</v>
+        <v>16700</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2700</v>
+        <v>-2800</v>
       </c>
       <c r="E18" s="3">
         <v>-1200</v>
       </c>
       <c r="F18" s="3">
-        <v>-5600</v>
+        <v>-5700</v>
       </c>
       <c r="G18" s="3">
-        <v>-6700</v>
+        <v>-6900</v>
       </c>
       <c r="H18" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="I18" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="J18" s="3">
-        <v>-1200</v>
+        <v>-1300</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1154,10 +1154,10 @@
         <v>-900</v>
       </c>
       <c r="G20" s="3">
-        <v>-2300</v>
+        <v>-2400</v>
       </c>
       <c r="H20" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="I20" s="3">
         <v>1200</v>
@@ -1186,22 +1186,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="E21" s="3">
         <v>300</v>
       </c>
       <c r="F21" s="3">
-        <v>-4700</v>
+        <v>-4900</v>
       </c>
       <c r="G21" s="3">
-        <v>-7300</v>
+        <v>-7500</v>
       </c>
       <c r="H21" s="3">
         <v>-500</v>
       </c>
       <c r="I21" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="J21" s="3">
         <v>100</v>
@@ -1274,19 +1274,19 @@
         <v>-1500</v>
       </c>
       <c r="F23" s="3">
-        <v>-6500</v>
+        <v>-6600</v>
       </c>
       <c r="G23" s="3">
-        <v>-9000</v>
+        <v>-9200</v>
       </c>
       <c r="H23" s="3">
-        <v>-2100</v>
+        <v>-2200</v>
       </c>
       <c r="I23" s="3">
-        <v>-3500</v>
+        <v>-3600</v>
       </c>
       <c r="J23" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1318,7 +1318,7 @@
         <v>-400</v>
       </c>
       <c r="G24" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="H24" s="3">
         <v>400</v>
@@ -1391,25 +1391,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E26" s="3">
         <v>-1200</v>
       </c>
       <c r="F26" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="G26" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="H26" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="I26" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="J26" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1432,25 +1432,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E27" s="3">
         <v>-1200</v>
       </c>
       <c r="F27" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="G27" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="H27" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="I27" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="J27" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1646,10 +1646,10 @@
         <v>900</v>
       </c>
       <c r="G32" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="H32" s="3">
-        <v>-2600</v>
+        <v>-2700</v>
       </c>
       <c r="I32" s="3">
         <v>-1200</v>
@@ -1678,25 +1678,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E33" s="3">
         <v>-1200</v>
       </c>
       <c r="F33" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="G33" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="H33" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="I33" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="J33" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1760,25 +1760,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E35" s="3">
         <v>-1200</v>
       </c>
       <c r="F35" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="G35" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="H35" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="I35" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="J35" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1881,25 +1881,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>17400</v>
+        <v>17800</v>
       </c>
       <c r="E41" s="3">
-        <v>23700</v>
+        <v>24300</v>
       </c>
       <c r="F41" s="3">
-        <v>13400</v>
+        <v>13800</v>
       </c>
       <c r="G41" s="3">
-        <v>12500</v>
+        <v>12800</v>
       </c>
       <c r="H41" s="3">
-        <v>11600</v>
+        <v>11800</v>
       </c>
       <c r="I41" s="3">
-        <v>23100</v>
+        <v>23600</v>
       </c>
       <c r="J41" s="3">
-        <v>41300</v>
+        <v>42400</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1928,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>12900</v>
+        <v>13200</v>
       </c>
       <c r="G42" s="3">
-        <v>20700</v>
+        <v>21200</v>
       </c>
       <c r="H42" s="3">
-        <v>30400</v>
+        <v>31100</v>
       </c>
       <c r="I42" s="3">
-        <v>21100</v>
+        <v>21600</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
@@ -1963,25 +1963,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>25400</v>
+        <v>26100</v>
       </c>
       <c r="E43" s="3">
-        <v>23700</v>
+        <v>24200</v>
       </c>
       <c r="F43" s="3">
-        <v>23200</v>
+        <v>23800</v>
       </c>
       <c r="G43" s="3">
-        <v>25700</v>
+        <v>26400</v>
       </c>
       <c r="H43" s="3">
-        <v>27900</v>
+        <v>28600</v>
       </c>
       <c r="I43" s="3">
-        <v>31100</v>
+        <v>31900</v>
       </c>
       <c r="J43" s="3">
-        <v>28100</v>
+        <v>28800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -2004,25 +2004,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6100</v>
+        <v>6300</v>
       </c>
       <c r="E44" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F44" s="3">
         <v>6300</v>
       </c>
-      <c r="F44" s="3">
-        <v>6100</v>
-      </c>
       <c r="G44" s="3">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="H44" s="3">
-        <v>8400</v>
+        <v>8600</v>
       </c>
       <c r="I44" s="3">
-        <v>8000</v>
+        <v>8200</v>
       </c>
       <c r="J44" s="3">
-        <v>7300</v>
+        <v>7500</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -2054,7 +2054,7 @@
         <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -2086,25 +2086,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>48900</v>
+        <v>50100</v>
       </c>
       <c r="E46" s="3">
-        <v>53700</v>
+        <v>55000</v>
       </c>
       <c r="F46" s="3">
-        <v>55600</v>
+        <v>57000</v>
       </c>
       <c r="G46" s="3">
-        <v>69400</v>
+        <v>71200</v>
       </c>
       <c r="H46" s="3">
-        <v>78200</v>
+        <v>80100</v>
       </c>
       <c r="I46" s="3">
-        <v>83300</v>
+        <v>85300</v>
       </c>
       <c r="J46" s="3">
-        <v>76800</v>
+        <v>78700</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2168,25 +2168,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>10800</v>
+        <v>11100</v>
       </c>
       <c r="E48" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F48" s="3">
         <v>10900</v>
       </c>
-      <c r="F48" s="3">
-        <v>10600</v>
-      </c>
       <c r="G48" s="3">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="H48" s="3">
-        <v>11000</v>
+        <v>11300</v>
       </c>
       <c r="I48" s="3">
-        <v>11500</v>
+        <v>11800</v>
       </c>
       <c r="J48" s="3">
-        <v>11600</v>
+        <v>11900</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2209,25 +2209,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>17600</v>
+        <v>18000</v>
       </c>
       <c r="E49" s="3">
-        <v>18700</v>
+        <v>19100</v>
       </c>
       <c r="F49" s="3">
-        <v>19600</v>
+        <v>20000</v>
       </c>
       <c r="G49" s="3">
-        <v>20500</v>
+        <v>21000</v>
       </c>
       <c r="H49" s="3">
-        <v>21700</v>
+        <v>22200</v>
       </c>
       <c r="I49" s="3">
-        <v>22200</v>
+        <v>22800</v>
       </c>
       <c r="J49" s="3">
-        <v>22800</v>
+        <v>23400</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2332,25 +2332,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="E52" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="F52" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="G52" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="H52" s="3">
         <v>2700</v>
       </c>
       <c r="I52" s="3">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="J52" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2414,25 +2414,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>82100</v>
+        <v>84100</v>
       </c>
       <c r="E54" s="3">
-        <v>87500</v>
+        <v>89700</v>
       </c>
       <c r="F54" s="3">
-        <v>89600</v>
+        <v>91800</v>
       </c>
       <c r="G54" s="3">
-        <v>104700</v>
+        <v>107300</v>
       </c>
       <c r="H54" s="3">
-        <v>113600</v>
+        <v>116400</v>
       </c>
       <c r="I54" s="3">
-        <v>120000</v>
+        <v>123000</v>
       </c>
       <c r="J54" s="3">
-        <v>113800</v>
+        <v>116700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2498,7 +2498,7 @@
         <v>3</v>
       </c>
       <c r="G57" s="3">
-        <v>8200</v>
+        <v>8400</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2530,25 +2530,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="E58" s="3">
         <v>2100</v>
       </c>
       <c r="F58" s="3">
-        <v>16800</v>
+        <v>17300</v>
       </c>
       <c r="G58" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="H58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I58" s="3">
         <v>2000</v>
       </c>
-      <c r="I58" s="3">
-        <v>1900</v>
-      </c>
       <c r="J58" s="3">
-        <v>18200</v>
+        <v>18600</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2571,25 +2571,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>27200</v>
+        <v>27900</v>
       </c>
       <c r="E59" s="3">
-        <v>26600</v>
+        <v>27300</v>
       </c>
       <c r="F59" s="3">
-        <v>12000</v>
+        <v>12300</v>
       </c>
       <c r="G59" s="3">
-        <v>26300</v>
+        <v>27000</v>
       </c>
       <c r="H59" s="3">
-        <v>33400</v>
+        <v>34300</v>
       </c>
       <c r="I59" s="3">
-        <v>38800</v>
+        <v>39700</v>
       </c>
       <c r="J59" s="3">
-        <v>13900</v>
+        <v>14200</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2612,25 +2612,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>29200</v>
+        <v>30000</v>
       </c>
       <c r="E60" s="3">
-        <v>28700</v>
+        <v>29400</v>
       </c>
       <c r="F60" s="3">
-        <v>28900</v>
+        <v>29600</v>
       </c>
       <c r="G60" s="3">
-        <v>36400</v>
+        <v>37300</v>
       </c>
       <c r="H60" s="3">
-        <v>35400</v>
+        <v>36300</v>
       </c>
       <c r="I60" s="3">
-        <v>40700</v>
+        <v>41700</v>
       </c>
       <c r="J60" s="3">
-        <v>32100</v>
+        <v>32800</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2653,25 +2653,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>43200</v>
+        <v>44300</v>
       </c>
       <c r="E61" s="3">
-        <v>46800</v>
+        <v>47900</v>
       </c>
       <c r="F61" s="3">
-        <v>48000</v>
+        <v>49200</v>
       </c>
       <c r="G61" s="3">
-        <v>49000</v>
+        <v>50200</v>
       </c>
       <c r="H61" s="3">
-        <v>49200</v>
+        <v>50400</v>
       </c>
       <c r="I61" s="3">
-        <v>49400</v>
+        <v>50700</v>
       </c>
       <c r="J61" s="3">
-        <v>49700</v>
+        <v>51000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2694,7 +2694,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
         <v>400</v>
@@ -2706,13 +2706,13 @@
         <v>1000</v>
       </c>
       <c r="H62" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="I62" s="3">
         <v>700</v>
       </c>
       <c r="J62" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2858,25 +2858,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>73400</v>
+        <v>75200</v>
       </c>
       <c r="E66" s="3">
-        <v>75800</v>
+        <v>77700</v>
       </c>
       <c r="F66" s="3">
-        <v>77400</v>
+        <v>79400</v>
       </c>
       <c r="G66" s="3">
-        <v>86400</v>
+        <v>88500</v>
       </c>
       <c r="H66" s="3">
-        <v>85500</v>
+        <v>87600</v>
       </c>
       <c r="I66" s="3">
-        <v>90800</v>
+        <v>93100</v>
       </c>
       <c r="J66" s="3">
-        <v>82700</v>
+        <v>84800</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -3244,25 +3244,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8700</v>
+        <v>8900</v>
       </c>
       <c r="E76" s="3">
-        <v>11700</v>
+        <v>12000</v>
       </c>
       <c r="F76" s="3">
-        <v>12200</v>
+        <v>12500</v>
       </c>
       <c r="G76" s="3">
-        <v>18300</v>
+        <v>18800</v>
       </c>
       <c r="H76" s="3">
-        <v>28200</v>
+        <v>28900</v>
       </c>
       <c r="I76" s="3">
-        <v>29200</v>
+        <v>29900</v>
       </c>
       <c r="J76" s="3">
-        <v>31100</v>
+        <v>31900</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3372,25 +3372,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="E81" s="3">
         <v>-1200</v>
       </c>
       <c r="F81" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="G81" s="3">
-        <v>-8700</v>
+        <v>-8900</v>
       </c>
       <c r="H81" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="I81" s="3">
-        <v>-3400</v>
+        <v>-3500</v>
       </c>
       <c r="J81" s="3">
-        <v>-2200</v>
+        <v>-2300</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3430,13 +3430,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="E83" s="3">
         <v>1800</v>
       </c>
       <c r="F83" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="G83" s="3">
         <v>1700</v>
@@ -3445,7 +3445,7 @@
         <v>1700</v>
       </c>
       <c r="I83" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="J83" s="3">
         <v>1500</v>
@@ -3679,22 +3679,22 @@
         <v>-2100</v>
       </c>
       <c r="E89" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="F89" s="3">
-        <v>-5800</v>
+        <v>-6000</v>
       </c>
       <c r="G89" s="3">
-        <v>-4600</v>
+        <v>-4700</v>
       </c>
       <c r="H89" s="3">
-        <v>-5700</v>
+        <v>-5900</v>
       </c>
       <c r="I89" s="3">
         <v>1400</v>
       </c>
       <c r="J89" s="3">
-        <v>-5800</v>
+        <v>-6000</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3860,19 +3860,19 @@
         <v>-600</v>
       </c>
       <c r="E94" s="3">
-        <v>11800</v>
+        <v>12100</v>
       </c>
       <c r="F94" s="3">
-        <v>7800</v>
+        <v>8000</v>
       </c>
       <c r="G94" s="3">
-        <v>6300</v>
+        <v>6400</v>
       </c>
       <c r="H94" s="3">
-        <v>-6500</v>
+        <v>-6700</v>
       </c>
       <c r="I94" s="3">
-        <v>-21400</v>
+        <v>-21900</v>
       </c>
       <c r="J94" s="3">
         <v>-500</v>
@@ -4079,16 +4079,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3700</v>
+        <v>-3800</v>
       </c>
       <c r="E100" s="3">
         <v>-1700</v>
       </c>
       <c r="F100" s="3">
-        <v>-700</v>
+        <v>-800</v>
       </c>
       <c r="G100" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="H100" s="3">
         <v>-500</v>
@@ -4135,7 +4135,7 @@
         <v>1200</v>
       </c>
       <c r="I101" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="J101" s="3">
         <v>600</v>
@@ -4161,25 +4161,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6300</v>
+        <v>-6500</v>
       </c>
       <c r="E102" s="3">
-        <v>10300</v>
+        <v>10500</v>
       </c>
       <c r="F102" s="3">
         <v>1000</v>
       </c>
       <c r="G102" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H102" s="3">
-        <v>-11500</v>
+        <v>-11800</v>
       </c>
       <c r="I102" s="3">
-        <v>-18300</v>
+        <v>-18700</v>
       </c>
       <c r="J102" s="3">
-        <v>-6300</v>
+        <v>-6400</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
   <si>
     <t>ORXOY</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -722,38 +723,44 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F8" s="3">
         <v>15100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
+        <v>15200</v>
+      </c>
+      <c r="H8" s="3">
         <v>15300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
+        <v>15100</v>
+      </c>
+      <c r="J8" s="3">
+        <v>15500</v>
+      </c>
+      <c r="K8" s="3">
+        <v>14300</v>
+      </c>
+      <c r="L8" s="3">
         <v>15400</v>
       </c>
-      <c r="G8" s="3">
-        <v>15100</v>
-      </c>
-      <c r="H8" s="3">
-        <v>15600</v>
-      </c>
-      <c r="I8" s="3">
-        <v>14300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>15400</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -763,37 +770,43 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F9" s="3">
         <v>2200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2100</v>
       </c>
       <c r="J9" s="3">
         <v>2700</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
+      <c r="K9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>2700</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
@@ -804,37 +817,43 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F10" s="3">
         <v>12900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>13600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>12600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>12600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>12900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>12200</v>
       </c>
       <c r="J10" s="3">
         <v>12800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
+      <c r="K10" s="3">
+        <v>12200</v>
+      </c>
+      <c r="L10" s="3">
+        <v>12800</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
@@ -845,8 +864,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,38 +887,40 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F12" s="3">
         <v>8100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>7300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>7600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>8500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>7400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>7900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>7000</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,8 +930,14 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,8 +977,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -976,17 +1015,23 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1017,17 +1062,23 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,38 +1091,40 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17900</v>
+        <v>13900</v>
       </c>
       <c r="E17" s="3">
+        <v>16900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>17800</v>
+      </c>
+      <c r="G17" s="3">
         <v>16500</v>
       </c>
-      <c r="F17" s="3">
-        <v>21100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>22000</v>
-      </c>
       <c r="H17" s="3">
-        <v>20400</v>
+        <v>21000</v>
       </c>
       <c r="I17" s="3">
+        <v>21900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>20300</v>
+      </c>
+      <c r="K17" s="3">
         <v>19100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>16700</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1081,38 +1134,44 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-5700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-6900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-4800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1122,8 +1181,14 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,38 +1204,40 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-2400</v>
       </c>
-      <c r="H20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,38 +1247,44 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-4900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,8 +1294,14 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1253,47 +1332,53 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-6600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-9200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1303,38 +1388,44 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1344,8 +1435,14 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,38 +1482,44 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-6200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-8900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1426,38 +1529,44 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-6200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-8900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,8 +1576,14 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1623,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1540,17 +1661,23 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1717,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,38 +1764,44 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F32" s="3">
         <v>800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>2400</v>
       </c>
-      <c r="H32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1672,38 +1811,44 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-6200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-8900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1713,8 +1858,14 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,38 +1905,44 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-6200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-8900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1795,43 +1952,49 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1841,8 +2004,14 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +2027,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,38 +2046,40 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F41" s="3">
         <v>17800</v>
       </c>
-      <c r="E41" s="3">
-        <v>24300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>13800</v>
-      </c>
       <c r="G41" s="3">
+        <v>24200</v>
+      </c>
+      <c r="H41" s="3">
+        <v>13700</v>
+      </c>
+      <c r="I41" s="3">
         <v>12800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>23600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>42400</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1916,8 +2089,14 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1928,23 +2107,23 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>13200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>21200</v>
       </c>
-      <c r="H42" s="3">
-        <v>31100</v>
-      </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K42" s="3">
         <v>21600</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1957,38 +2136,44 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>26100</v>
+        <v>23500</v>
       </c>
       <c r="E43" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>26000</v>
+      </c>
+      <c r="G43" s="3">
         <v>24200</v>
       </c>
-      <c r="F43" s="3">
-        <v>23800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>26400</v>
-      </c>
       <c r="H43" s="3">
-        <v>28600</v>
+        <v>23700</v>
       </c>
       <c r="I43" s="3">
+        <v>26300</v>
+      </c>
+      <c r="J43" s="3">
+        <v>28500</v>
+      </c>
+      <c r="K43" s="3">
         <v>31900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>28800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1998,38 +2183,44 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6300</v>
+        <v>6900</v>
       </c>
       <c r="E44" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F44" s="3">
+        <v>6200</v>
+      </c>
+      <c r="G44" s="3">
         <v>6500</v>
       </c>
-      <c r="F44" s="3">
-        <v>6300</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I44" s="3">
         <v>7200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>8600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>8200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>7500</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,28 +2230,34 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="E45" s="3">
+        <v>3200</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
-        <v>3600</v>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3">
+        <v>3500</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2080,38 +2277,44 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>50100</v>
+        <v>49500</v>
       </c>
       <c r="E46" s="3">
-        <v>55000</v>
+        <v>44300</v>
       </c>
       <c r="F46" s="3">
-        <v>57000</v>
+        <v>50000</v>
       </c>
       <c r="G46" s="3">
-        <v>71200</v>
+        <v>54900</v>
       </c>
       <c r="H46" s="3">
-        <v>80100</v>
+        <v>56900</v>
       </c>
       <c r="I46" s="3">
+        <v>71000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>79900</v>
+      </c>
+      <c r="K46" s="3">
         <v>85300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>78700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,8 +2324,14 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2130,13 +2339,13 @@
         <v>100</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F47" s="3">
         <v>100</v>
       </c>
       <c r="G47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
         <v>100</v>
@@ -2147,11 +2356,11 @@
       <c r="J47" s="3">
         <v>100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
+      <c r="K47" s="3">
+        <v>100</v>
+      </c>
+      <c r="L47" s="3">
+        <v>100</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
@@ -2162,38 +2371,44 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F48" s="3">
         <v>11100</v>
       </c>
-      <c r="E48" s="3">
-        <v>11200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>10900</v>
-      </c>
       <c r="G48" s="3">
-        <v>11800</v>
+        <v>11100</v>
       </c>
       <c r="H48" s="3">
-        <v>11300</v>
+        <v>10800</v>
       </c>
       <c r="I48" s="3">
         <v>11800</v>
       </c>
       <c r="J48" s="3">
+        <v>11300</v>
+      </c>
+      <c r="K48" s="3">
+        <v>11800</v>
+      </c>
+      <c r="L48" s="3">
         <v>11900</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,38 +2418,44 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F49" s="3">
         <v>18000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>19100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>20000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>21000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>22200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>22800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>23400</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,8 +2465,14 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2512,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,38 +2559,44 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="E52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G52" s="3">
         <v>4300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,8 +2606,14 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,38 +2653,44 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>84100</v>
+        <v>80100</v>
       </c>
       <c r="E54" s="3">
-        <v>89700</v>
+        <v>75900</v>
       </c>
       <c r="F54" s="3">
-        <v>91800</v>
+        <v>83900</v>
       </c>
       <c r="G54" s="3">
-        <v>107300</v>
+        <v>89500</v>
       </c>
       <c r="H54" s="3">
-        <v>116400</v>
+        <v>91600</v>
       </c>
       <c r="I54" s="3">
+        <v>107000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>116100</v>
+      </c>
+      <c r="K54" s="3">
         <v>123000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>116700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,8 +2700,14 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2723,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,29 +2742,31 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
+      <c r="E57" s="3">
+        <v>3500</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>8400</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,38 +2785,44 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2100</v>
       </c>
-      <c r="F58" s="3">
-        <v>17300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2000</v>
-      </c>
       <c r="H58" s="3">
-        <v>2100</v>
+        <v>17200</v>
       </c>
       <c r="I58" s="3">
         <v>2000</v>
       </c>
       <c r="J58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L58" s="3">
         <v>18600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2565,38 +2832,44 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>27900</v>
+        <v>22500</v>
       </c>
       <c r="E59" s="3">
-        <v>27300</v>
+        <v>19900</v>
       </c>
       <c r="F59" s="3">
+        <v>27800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>27200</v>
+      </c>
+      <c r="H59" s="3">
         <v>12300</v>
       </c>
-      <c r="G59" s="3">
-        <v>27000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>34300</v>
-      </c>
       <c r="I59" s="3">
+        <v>26900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>34200</v>
+      </c>
+      <c r="K59" s="3">
         <v>39700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>14200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,38 +2879,44 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>30000</v>
+        <v>72300</v>
       </c>
       <c r="E60" s="3">
-        <v>29400</v>
+        <v>25400</v>
       </c>
       <c r="F60" s="3">
-        <v>29600</v>
+        <v>29900</v>
       </c>
       <c r="G60" s="3">
-        <v>37300</v>
+        <v>29300</v>
       </c>
       <c r="H60" s="3">
-        <v>36300</v>
+        <v>29500</v>
       </c>
       <c r="I60" s="3">
+        <v>37200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>36200</v>
+      </c>
+      <c r="K60" s="3">
         <v>41700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>32800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,38 +2926,44 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>44300</v>
+        <v>600</v>
       </c>
       <c r="E61" s="3">
-        <v>47900</v>
+        <v>43700</v>
       </c>
       <c r="F61" s="3">
-        <v>49200</v>
+        <v>44100</v>
       </c>
       <c r="G61" s="3">
-        <v>50200</v>
+        <v>47800</v>
       </c>
       <c r="H61" s="3">
-        <v>50400</v>
+        <v>49000</v>
       </c>
       <c r="I61" s="3">
+        <v>50100</v>
+      </c>
+      <c r="J61" s="3">
+        <v>50300</v>
+      </c>
+      <c r="K61" s="3">
         <v>50700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>51000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2688,38 +2973,44 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,8 +3020,14 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +3067,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +3114,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,38 +3161,44 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>75200</v>
+        <v>74200</v>
       </c>
       <c r="E66" s="3">
-        <v>77700</v>
+        <v>70200</v>
       </c>
       <c r="F66" s="3">
-        <v>79400</v>
+        <v>75000</v>
       </c>
       <c r="G66" s="3">
-        <v>88500</v>
+        <v>77500</v>
       </c>
       <c r="H66" s="3">
-        <v>87600</v>
+        <v>79200</v>
       </c>
       <c r="I66" s="3">
+        <v>88300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>87400</v>
+      </c>
+      <c r="K66" s="3">
         <v>93100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>84800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,8 +3208,14 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3231,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3274,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3321,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3024,17 +3359,23 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>3</v>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,8 +3415,14 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3106,17 +3453,23 @@
       <c r="L72" s="3">
         <v>0</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3">
+        <v>0</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3509,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3556,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,38 +3603,44 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F76" s="3">
         <v>8900</v>
       </c>
-      <c r="E76" s="3">
-        <v>12000</v>
-      </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>11900</v>
+      </c>
+      <c r="H76" s="3">
         <v>12500</v>
       </c>
-      <c r="G76" s="3">
-        <v>18800</v>
-      </c>
-      <c r="H76" s="3">
-        <v>28900</v>
-      </c>
       <c r="I76" s="3">
+        <v>18700</v>
+      </c>
+      <c r="J76" s="3">
+        <v>28800</v>
+      </c>
+      <c r="K76" s="3">
         <v>29900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>31900</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3279,8 +3650,14 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,43 +3697,49 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3366,38 +3749,44 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-6200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-8900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3407,8 +3796,14 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,38 +3819,40 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1700</v>
       </c>
       <c r="I83" s="3">
         <v>1700</v>
       </c>
       <c r="J83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3465,8 +3862,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3909,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3956,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +4003,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +4050,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,38 +4097,44 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-4700</v>
       </c>
       <c r="H89" s="3">
         <v>-5900</v>
       </c>
       <c r="I89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="K89" s="3">
         <v>1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,8 +4144,14 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,49 +4167,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-6700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-10800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-12300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-4500</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4257,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,38 +4304,44 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>12100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>8000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>6400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-6700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-21900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3892,8 +4351,14 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4374,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3950,8 +4417,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4464,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4511,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,37 +4558,43 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-3800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-500</v>
       </c>
       <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-500</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -4114,38 +4605,44 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4155,38 +4652,44 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6500</v>
+        <v>2600</v>
       </c>
       <c r="E102" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="G102" s="3">
         <v>10500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-11800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-18700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6400</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4194,6 +4697,12 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
   <si>
     <t>ORXOY</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -729,41 +730,44 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>13400</v>
+        <v>15100</v>
       </c>
       <c r="E8" s="3">
-        <v>16000</v>
+        <v>13600</v>
       </c>
       <c r="F8" s="3">
-        <v>15100</v>
+        <v>16300</v>
       </c>
       <c r="G8" s="3">
-        <v>15200</v>
+        <v>15300</v>
       </c>
       <c r="H8" s="3">
+        <v>15400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>15600</v>
+      </c>
+      <c r="J8" s="3">
         <v>15300</v>
       </c>
-      <c r="I8" s="3">
-        <v>15100</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15400</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -776,41 +780,44 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1300</v>
       </c>
-      <c r="E9" s="3">
-        <v>1900</v>
-      </c>
       <c r="F9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3">
         <v>2200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2700</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,41 +830,44 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>14300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>12700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K10" s="3">
+        <v>12800</v>
+      </c>
+      <c r="L10" s="3">
         <v>12200</v>
       </c>
-      <c r="E10" s="3">
-        <v>14100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>12900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>13600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>12600</v>
-      </c>
-      <c r="I10" s="3">
-        <v>12600</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>12800</v>
       </c>
-      <c r="K10" s="3">
-        <v>12200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>12800</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,8 +880,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,41 +902,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E12" s="3">
         <v>5500</v>
       </c>
-      <c r="E12" s="3">
-        <v>6300</v>
-      </c>
       <c r="F12" s="3">
-        <v>8100</v>
+        <v>6400</v>
       </c>
       <c r="G12" s="3">
-        <v>7300</v>
+        <v>8200</v>
       </c>
       <c r="H12" s="3">
-        <v>7600</v>
+        <v>7400</v>
       </c>
       <c r="I12" s="3">
-        <v>8500</v>
+        <v>7700</v>
       </c>
       <c r="J12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K12" s="3">
         <v>7400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -936,8 +950,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,8 +1000,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1021,8 +1041,8 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1030,8 +1050,11 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1068,8 +1091,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1077,8 +1100,11 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1093,41 +1119,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>13900</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>16900</v>
+        <v>14100</v>
       </c>
       <c r="F17" s="3">
-        <v>17800</v>
+        <v>17100</v>
       </c>
       <c r="G17" s="3">
-        <v>16500</v>
+        <v>18100</v>
       </c>
       <c r="H17" s="3">
-        <v>21000</v>
+        <v>16700</v>
       </c>
       <c r="I17" s="3">
-        <v>21900</v>
+        <v>21400</v>
       </c>
       <c r="J17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="K17" s="3">
         <v>20300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>19100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16700</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1140,41 +1167,44 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2800</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1200</v>
-      </c>
       <c r="H18" s="3">
-        <v>-5700</v>
+        <v>-1300</v>
       </c>
       <c r="I18" s="3">
-        <v>-6900</v>
+        <v>-5800</v>
       </c>
       <c r="J18" s="3">
-        <v>-4800</v>
+        <v>-7000</v>
       </c>
       <c r="K18" s="3">
         <v>-4800</v>
       </c>
       <c r="L18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1217,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1206,41 +1239,42 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,41 +1287,44 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1000</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-4900</v>
       </c>
-      <c r="I21" s="3">
-        <v>-7500</v>
-      </c>
       <c r="J21" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,8 +1337,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1338,8 +1378,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1347,41 +1387,44 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-900</v>
+        <v>-3700</v>
       </c>
       <c r="E23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
-        <v>-3500</v>
-      </c>
       <c r="G23" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="H23" s="3">
-        <v>-6600</v>
-      </c>
       <c r="I23" s="3">
-        <v>-9200</v>
+        <v>-6700</v>
       </c>
       <c r="J23" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1394,8 +1437,11 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1406,29 +1452,29 @@
         <v>-100</v>
       </c>
       <c r="F24" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="G24" s="3">
         <v>-300</v>
       </c>
       <c r="H24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,8 +1487,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1488,41 +1537,44 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-3200</v>
-      </c>
       <c r="G26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
-        <v>-6200</v>
-      </c>
       <c r="I26" s="3">
-        <v>-8900</v>
+        <v>-6300</v>
       </c>
       <c r="J26" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1535,41 +1587,44 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1800</v>
       </c>
-      <c r="F27" s="3">
-        <v>-3200</v>
-      </c>
       <c r="G27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
-        <v>-6200</v>
-      </c>
       <c r="I27" s="3">
-        <v>-8900</v>
+        <v>-6300</v>
       </c>
       <c r="J27" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,8 +1637,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1629,8 +1687,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1667,8 +1728,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>3</v>
@@ -1676,8 +1737,11 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1723,8 +1787,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1770,41 +1837,44 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,41 +1887,44 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1800</v>
       </c>
-      <c r="F33" s="3">
-        <v>-3200</v>
-      </c>
       <c r="G33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
-        <v>-6200</v>
-      </c>
       <c r="I33" s="3">
-        <v>-8900</v>
+        <v>-6300</v>
       </c>
       <c r="J33" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,8 +1937,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1911,41 +1987,44 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1800</v>
       </c>
-      <c r="F35" s="3">
-        <v>-3200</v>
-      </c>
       <c r="G35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
-        <v>-6200</v>
-      </c>
       <c r="I35" s="3">
-        <v>-8900</v>
+        <v>-6300</v>
       </c>
       <c r="J35" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1958,46 +2037,49 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2010,8 +2092,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2029,8 +2114,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2048,41 +2134,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>19100</v>
+        <v>13700</v>
       </c>
       <c r="E41" s="3">
-        <v>16500</v>
+        <v>19400</v>
       </c>
       <c r="F41" s="3">
-        <v>17800</v>
+        <v>16700</v>
       </c>
       <c r="G41" s="3">
-        <v>24200</v>
+        <v>18000</v>
       </c>
       <c r="H41" s="3">
-        <v>13700</v>
+        <v>24600</v>
       </c>
       <c r="I41" s="3">
-        <v>12800</v>
+        <v>13900</v>
       </c>
       <c r="J41" s="3">
+        <v>12900</v>
+      </c>
+      <c r="K41" s="3">
         <v>11800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42400</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,13 +2182,16 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2113,20 +2203,20 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>13200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>21200</v>
+        <v>13400</v>
       </c>
       <c r="J42" s="3">
+        <v>21500</v>
+      </c>
+      <c r="K42" s="3">
         <v>31000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21600</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2142,41 +2232,44 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>23500</v>
+        <v>25200</v>
       </c>
       <c r="E43" s="3">
-        <v>20500</v>
+        <v>23800</v>
       </c>
       <c r="F43" s="3">
-        <v>26000</v>
+        <v>20800</v>
       </c>
       <c r="G43" s="3">
-        <v>24200</v>
+        <v>26400</v>
       </c>
       <c r="H43" s="3">
-        <v>23700</v>
+        <v>24500</v>
       </c>
       <c r="I43" s="3">
-        <v>26300</v>
+        <v>24100</v>
       </c>
       <c r="J43" s="3">
+        <v>26700</v>
+      </c>
+      <c r="K43" s="3">
         <v>28500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>31900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>28800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,41 +2282,44 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="E44" s="3">
-        <v>4100</v>
+        <v>7000</v>
       </c>
       <c r="F44" s="3">
-        <v>6200</v>
+        <v>4200</v>
       </c>
       <c r="G44" s="3">
-        <v>6500</v>
+        <v>6300</v>
       </c>
       <c r="H44" s="3">
-        <v>6200</v>
+        <v>6600</v>
       </c>
       <c r="I44" s="3">
-        <v>7200</v>
+        <v>6300</v>
       </c>
       <c r="J44" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K44" s="3">
         <v>8600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7500</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2236,31 +2332,34 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>3200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3600</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2283,41 +2382,44 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>49500</v>
+        <v>45700</v>
       </c>
       <c r="E46" s="3">
-        <v>44300</v>
+        <v>50200</v>
       </c>
       <c r="F46" s="3">
-        <v>50000</v>
+        <v>44900</v>
       </c>
       <c r="G46" s="3">
-        <v>54900</v>
+        <v>50700</v>
       </c>
       <c r="H46" s="3">
-        <v>56900</v>
+        <v>55700</v>
       </c>
       <c r="I46" s="3">
-        <v>71000</v>
+        <v>57700</v>
       </c>
       <c r="J46" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K46" s="3">
         <v>79900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>85300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>78700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2330,8 +2432,11 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2345,10 +2450,10 @@
         <v>100</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
         <v>100</v>
@@ -2362,8 +2467,8 @@
       <c r="L47" s="3">
         <v>100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
+      <c r="M47" s="3">
+        <v>100</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
@@ -2377,8 +2482,11 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2386,32 +2494,32 @@
         <v>9600</v>
       </c>
       <c r="E48" s="3">
-        <v>10200</v>
+        <v>9800</v>
       </c>
       <c r="F48" s="3">
-        <v>11100</v>
+        <v>10300</v>
       </c>
       <c r="G48" s="3">
-        <v>11100</v>
+        <v>11200</v>
       </c>
       <c r="H48" s="3">
-        <v>10800</v>
+        <v>11300</v>
       </c>
       <c r="I48" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K48" s="3">
+        <v>11300</v>
+      </c>
+      <c r="L48" s="3">
         <v>11800</v>
       </c>
-      <c r="J48" s="3">
-        <v>11300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>11800</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11900</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,41 +2532,44 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>16000</v>
+        <v>15100</v>
       </c>
       <c r="E49" s="3">
-        <v>16700</v>
+        <v>16200</v>
       </c>
       <c r="F49" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="G49" s="3">
-        <v>19100</v>
+        <v>18300</v>
       </c>
       <c r="H49" s="3">
-        <v>20000</v>
+        <v>19400</v>
       </c>
       <c r="I49" s="3">
-        <v>21000</v>
+        <v>20300</v>
       </c>
       <c r="J49" s="3">
+        <v>21300</v>
+      </c>
+      <c r="K49" s="3">
         <v>22200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23400</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2582,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2518,8 +2632,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2565,41 +2682,44 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4900</v>
+        <v>5200</v>
       </c>
       <c r="E52" s="3">
-        <v>4600</v>
+        <v>5000</v>
       </c>
       <c r="F52" s="3">
         <v>4700</v>
       </c>
       <c r="G52" s="3">
-        <v>4300</v>
+        <v>4800</v>
       </c>
       <c r="H52" s="3">
-        <v>3800</v>
+        <v>4400</v>
       </c>
       <c r="I52" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J52" s="3">
         <v>3200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2600</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,8 +2732,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2659,41 +2782,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>80100</v>
+        <v>75700</v>
       </c>
       <c r="E54" s="3">
-        <v>75900</v>
+        <v>81300</v>
       </c>
       <c r="F54" s="3">
-        <v>83900</v>
+        <v>77000</v>
       </c>
       <c r="G54" s="3">
-        <v>89500</v>
+        <v>85100</v>
       </c>
       <c r="H54" s="3">
-        <v>91600</v>
+        <v>90800</v>
       </c>
       <c r="I54" s="3">
-        <v>107000</v>
+        <v>93000</v>
       </c>
       <c r="J54" s="3">
+        <v>108600</v>
+      </c>
+      <c r="K54" s="3">
         <v>116100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>123000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>116700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2706,8 +2832,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2725,8 +2854,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2744,19 +2874,20 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3">
+        <v>3600</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>3</v>
@@ -2764,11 +2895,11 @@
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I57" s="3">
-        <v>8400</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
+        <v>8500</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2791,28 +2922,31 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>49800</v>
+        <v>1600</v>
       </c>
       <c r="E58" s="3">
+        <v>50600</v>
+      </c>
+      <c r="F58" s="3">
         <v>2000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>2100</v>
       </c>
       <c r="G58" s="3">
         <v>2100</v>
       </c>
       <c r="H58" s="3">
-        <v>17200</v>
+        <v>2100</v>
       </c>
       <c r="I58" s="3">
-        <v>2000</v>
+        <v>17500</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
@@ -2821,11 +2955,11 @@
         <v>2000</v>
       </c>
       <c r="L58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M58" s="3">
         <v>18600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,41 +2972,44 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>22500</v>
+        <v>24200</v>
       </c>
       <c r="E59" s="3">
-        <v>19900</v>
+        <v>22800</v>
       </c>
       <c r="F59" s="3">
-        <v>27800</v>
+        <v>20200</v>
       </c>
       <c r="G59" s="3">
-        <v>27200</v>
+        <v>28200</v>
       </c>
       <c r="H59" s="3">
-        <v>12300</v>
+        <v>27600</v>
       </c>
       <c r="I59" s="3">
-        <v>26900</v>
+        <v>12500</v>
       </c>
       <c r="J59" s="3">
+        <v>27300</v>
+      </c>
+      <c r="K59" s="3">
         <v>34200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2885,41 +3022,44 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>72300</v>
+        <v>25800</v>
       </c>
       <c r="E60" s="3">
-        <v>25400</v>
+        <v>73400</v>
       </c>
       <c r="F60" s="3">
+        <v>25800</v>
+      </c>
+      <c r="G60" s="3">
+        <v>30300</v>
+      </c>
+      <c r="H60" s="3">
+        <v>29800</v>
+      </c>
+      <c r="I60" s="3">
         <v>29900</v>
       </c>
-      <c r="G60" s="3">
-        <v>29300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>29500</v>
-      </c>
-      <c r="I60" s="3">
-        <v>37200</v>
-      </c>
       <c r="J60" s="3">
+        <v>37800</v>
+      </c>
+      <c r="K60" s="3">
         <v>36200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>41700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2932,41 +3072,44 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E61" s="3">
         <v>600</v>
       </c>
-      <c r="E61" s="3">
-        <v>43700</v>
-      </c>
       <c r="F61" s="3">
-        <v>44100</v>
+        <v>44400</v>
       </c>
       <c r="G61" s="3">
-        <v>47800</v>
+        <v>44800</v>
       </c>
       <c r="H61" s="3">
-        <v>49000</v>
+        <v>48500</v>
       </c>
       <c r="I61" s="3">
-        <v>50100</v>
+        <v>49800</v>
       </c>
       <c r="J61" s="3">
+        <v>50800</v>
+      </c>
+      <c r="K61" s="3">
         <v>50300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2979,41 +3122,44 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,8 +3172,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3073,8 +3222,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3120,8 +3272,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3167,41 +3322,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>74200</v>
+        <v>73400</v>
       </c>
       <c r="E66" s="3">
-        <v>70200</v>
+        <v>75300</v>
       </c>
       <c r="F66" s="3">
-        <v>75000</v>
+        <v>71300</v>
       </c>
       <c r="G66" s="3">
-        <v>77500</v>
+        <v>76100</v>
       </c>
       <c r="H66" s="3">
-        <v>79200</v>
+        <v>78700</v>
       </c>
       <c r="I66" s="3">
-        <v>88300</v>
+        <v>80300</v>
       </c>
       <c r="J66" s="3">
+        <v>89600</v>
+      </c>
+      <c r="K66" s="3">
         <v>87400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>93100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>84800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3214,8 +3372,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3233,8 +3394,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3280,8 +3442,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3327,8 +3492,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3365,8 +3533,8 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3" t="s">
-        <v>3</v>
+      <c r="O70" s="3">
+        <v>0</v>
       </c>
       <c r="P70" s="3" t="s">
         <v>3</v>
@@ -3374,8 +3542,11 @@
       <c r="Q70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3421,8 +3592,11 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3459,8 +3633,8 @@
       <c r="N72" s="3">
         <v>0</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
+      <c r="O72" s="3">
+        <v>0</v>
       </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
@@ -3468,8 +3642,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3515,8 +3692,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3562,8 +3742,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3609,41 +3792,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5900</v>
+        <v>2400</v>
       </c>
       <c r="E76" s="3">
-        <v>5700</v>
+        <v>6000</v>
       </c>
       <c r="F76" s="3">
-        <v>8900</v>
+        <v>5800</v>
       </c>
       <c r="G76" s="3">
-        <v>11900</v>
+        <v>9000</v>
       </c>
       <c r="H76" s="3">
-        <v>12500</v>
+        <v>12100</v>
       </c>
       <c r="I76" s="3">
-        <v>18700</v>
+        <v>12600</v>
       </c>
       <c r="J76" s="3">
+        <v>19000</v>
+      </c>
+      <c r="K76" s="3">
         <v>28800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31900</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3656,8 +3842,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3703,46 +3892,49 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3755,41 +3947,44 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1800</v>
       </c>
-      <c r="F81" s="3">
-        <v>-3200</v>
-      </c>
       <c r="G81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
-        <v>-6200</v>
-      </c>
       <c r="I81" s="3">
-        <v>-8900</v>
+        <v>-6300</v>
       </c>
       <c r="J81" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,8 +3997,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3821,41 +4019,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>2000</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E83" s="3">
         <v>2000</v>
       </c>
       <c r="F83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G83" s="3">
         <v>1900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1800</v>
       </c>
       <c r="H83" s="3">
         <v>1800</v>
       </c>
       <c r="I83" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="J83" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="K83" s="3">
         <v>1700</v>
       </c>
       <c r="L83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,8 +4067,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3915,8 +4117,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3962,8 +4167,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4009,8 +4217,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4056,8 +4267,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4103,41 +4317,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-1800</v>
+        <v>-600</v>
       </c>
       <c r="E89" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="K89" s="3">
         <v>-5900</v>
       </c>
-      <c r="I89" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4150,8 +4367,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4169,46 +4389,47 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4216,8 +4437,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4263,8 +4487,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4310,41 +4537,44 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
-        <v>12100</v>
-      </c>
       <c r="H94" s="3">
-        <v>8000</v>
+        <v>12300</v>
       </c>
       <c r="I94" s="3">
-        <v>6400</v>
+        <v>8100</v>
       </c>
       <c r="J94" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-6700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4357,8 +4587,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4376,8 +4609,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4423,8 +4657,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4470,8 +4707,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4517,8 +4757,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4564,31 +4807,34 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E100" s="3">
         <v>4200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-500</v>
       </c>
       <c r="K100" s="3">
         <v>-500</v>
@@ -4596,8 +4842,8 @@
       <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>-500</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
@@ -4611,41 +4857,44 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
-        <v>-300</v>
-      </c>
       <c r="I101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4658,41 +4907,44 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E102" s="3">
         <v>2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1300</v>
       </c>
-      <c r="F102" s="3">
-        <v>-6400</v>
-      </c>
       <c r="G102" s="3">
-        <v>10500</v>
+        <v>-6500</v>
       </c>
       <c r="H102" s="3">
-        <v>1000</v>
+        <v>10600</v>
       </c>
       <c r="I102" s="3">
         <v>1000</v>
       </c>
       <c r="J102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-11800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6400</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,6 +4955,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="92">
   <si>
     <t>ORXOY</t>
   </si>
@@ -656,71 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -733,44 +734,47 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>15100</v>
-      </c>
-      <c r="E8" s="3">
-        <v>13600</v>
-      </c>
-      <c r="F8" s="3">
-        <v>16300</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>15300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
+        <v>15500</v>
+      </c>
+      <c r="M8" s="3">
+        <v>14300</v>
+      </c>
+      <c r="N8" s="3">
         <v>15400</v>
       </c>
-      <c r="I8" s="3">
-        <v>15600</v>
-      </c>
-      <c r="J8" s="3">
-        <v>15300</v>
-      </c>
-      <c r="K8" s="3">
-        <v>15500</v>
-      </c>
-      <c r="L8" s="3">
-        <v>14300</v>
-      </c>
-      <c r="M8" s="3">
-        <v>15400</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,44 +787,47 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
-        <v>1600</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>2500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2700</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -833,44 +840,47 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>13500</v>
-      </c>
-      <c r="E10" s="3">
-        <v>12300</v>
-      </c>
-      <c r="F10" s="3">
-        <v>14300</v>
-      </c>
-      <c r="G10" s="3">
-        <v>13100</v>
-      </c>
-      <c r="H10" s="3">
-        <v>13800</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>12700</v>
       </c>
-      <c r="J10" s="3">
-        <v>12700</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -883,8 +893,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,44 +916,45 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>6300</v>
-      </c>
-      <c r="E12" s="3">
-        <v>5500</v>
-      </c>
-      <c r="F12" s="3">
-        <v>6400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>8200</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
+        <v>8600</v>
+      </c>
+      <c r="L12" s="3">
         <v>7400</v>
       </c>
-      <c r="I12" s="3">
-        <v>7700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>8600</v>
-      </c>
-      <c r="K12" s="3">
-        <v>7400</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7000</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -953,8 +967,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1003,31 +1020,34 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1044,8 +1064,8 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1053,31 +1073,34 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1094,8 +1117,8 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
@@ -1103,8 +1126,11 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1120,44 +1146,45 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="3">
-        <v>14100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>17100</v>
-      </c>
-      <c r="G17" s="3">
-        <v>18100</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="E17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
+        <v>22200</v>
+      </c>
+      <c r="L17" s="3">
+        <v>20300</v>
+      </c>
+      <c r="M17" s="3">
+        <v>19100</v>
+      </c>
+      <c r="N17" s="3">
         <v>16700</v>
       </c>
-      <c r="I17" s="3">
-        <v>21400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>22200</v>
-      </c>
-      <c r="K17" s="3">
-        <v>20300</v>
-      </c>
-      <c r="L17" s="3">
-        <v>19100</v>
-      </c>
-      <c r="M17" s="3">
-        <v>16700</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1170,44 +1197,47 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="3">
-        <v>-500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="E18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>-7000</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-4800</v>
       </c>
       <c r="L18" s="3">
         <v>-4800</v>
       </c>
       <c r="M18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1220,8 +1250,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1240,44 +1273,45 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-900</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,44 +1324,47 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="N21" s="3">
         <v>100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H21" s="3">
-        <v>300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-7600</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>100</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1340,31 +1377,34 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1381,8 +1421,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
@@ -1390,44 +1430,47 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M23" s="3">
         <v>-3600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="N23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,44 +1483,47 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1490,8 +1536,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1540,44 +1589,47 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="E26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
         <v>-9000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1590,44 +1642,47 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
         <v>-9000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1640,8 +1695,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1690,31 +1748,34 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1731,8 +1792,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
@@ -1740,8 +1801,11 @@
       <c r="R29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1790,8 +1854,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1840,44 +1907,47 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>900</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>2400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1890,44 +1960,47 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
         <v>-9000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1940,8 +2013,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1990,44 +2066,47 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
         <v>-9000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,49 +2119,52 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2177,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2115,8 +2200,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2135,44 +2221,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13700</v>
+        <v>11300</v>
       </c>
       <c r="E41" s="3">
-        <v>19400</v>
+        <v>13200</v>
       </c>
       <c r="F41" s="3">
-        <v>16700</v>
+        <v>18500</v>
       </c>
       <c r="G41" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="H41" s="3">
-        <v>24600</v>
+        <v>16900</v>
       </c>
       <c r="I41" s="3">
-        <v>13900</v>
+        <v>23300</v>
       </c>
       <c r="J41" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K41" s="3">
         <v>12900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42400</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,13 +2272,16 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2206,20 +2296,20 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>13400</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K42" s="3">
         <v>21500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>31000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21600</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,44 +2325,47 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>25200</v>
+        <v>24200</v>
       </c>
       <c r="E43" s="3">
-        <v>23800</v>
+        <v>24300</v>
       </c>
       <c r="F43" s="3">
-        <v>20800</v>
+        <v>22800</v>
       </c>
       <c r="G43" s="3">
-        <v>26400</v>
+        <v>21200</v>
       </c>
       <c r="H43" s="3">
-        <v>24500</v>
+        <v>24700</v>
       </c>
       <c r="I43" s="3">
-        <v>24100</v>
+        <v>23200</v>
       </c>
       <c r="J43" s="3">
+        <v>23700</v>
+      </c>
+      <c r="K43" s="3">
         <v>26700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>28500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>31900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>28800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,44 +2378,47 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>6800</v>
+        <v>5400</v>
       </c>
       <c r="E44" s="3">
-        <v>7000</v>
+        <v>6500</v>
       </c>
       <c r="F44" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G44" s="3">
         <v>4200</v>
       </c>
-      <c r="G44" s="3">
-        <v>6300</v>
-      </c>
       <c r="H44" s="3">
-        <v>6600</v>
+        <v>5900</v>
       </c>
       <c r="I44" s="3">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="J44" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K44" s="3">
         <v>7300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7500</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2335,8 +2431,11 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2346,11 +2445,11 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -2358,12 +2457,12 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2385,44 +2484,47 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>45700</v>
+        <v>40900</v>
       </c>
       <c r="E46" s="3">
-        <v>50200</v>
+        <v>44000</v>
       </c>
       <c r="F46" s="3">
-        <v>44900</v>
+        <v>48000</v>
       </c>
       <c r="G46" s="3">
-        <v>50700</v>
+        <v>45600</v>
       </c>
       <c r="H46" s="3">
-        <v>55700</v>
+        <v>47500</v>
       </c>
       <c r="I46" s="3">
-        <v>57700</v>
+        <v>52700</v>
       </c>
       <c r="J46" s="3">
+        <v>56900</v>
+      </c>
+      <c r="K46" s="3">
         <v>72000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>79900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>85300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>78700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,31 +2537,34 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>100</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>100</v>
@@ -2470,8 +2575,8 @@
       <c r="M47" s="3">
         <v>100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>100</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2485,44 +2590,47 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9600</v>
+        <v>8800</v>
       </c>
       <c r="E48" s="3">
-        <v>9800</v>
+        <v>9300</v>
       </c>
       <c r="F48" s="3">
-        <v>10300</v>
+        <v>9300</v>
       </c>
       <c r="G48" s="3">
-        <v>11200</v>
+        <v>10500</v>
       </c>
       <c r="H48" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K48" s="3">
+        <v>12000</v>
+      </c>
+      <c r="L48" s="3">
         <v>11300</v>
       </c>
-      <c r="I48" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>12000</v>
-      </c>
-      <c r="K48" s="3">
-        <v>11300</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11900</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,44 +2643,47 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>15100</v>
+        <v>14100</v>
       </c>
       <c r="E49" s="3">
-        <v>16200</v>
+        <v>14600</v>
       </c>
       <c r="F49" s="3">
-        <v>17000</v>
+        <v>15500</v>
       </c>
       <c r="G49" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>17100</v>
+      </c>
+      <c r="I49" s="3">
         <v>18300</v>
       </c>
-      <c r="H49" s="3">
-        <v>19400</v>
-      </c>
-      <c r="I49" s="3">
-        <v>20300</v>
-      </c>
       <c r="J49" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K49" s="3">
         <v>21300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>22200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>22800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23400</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2585,8 +2696,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2635,8 +2749,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2685,44 +2802,47 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>4700</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>4800</v>
+        <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>4400</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2600</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +2855,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2785,44 +2908,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>75700</v>
+        <v>68700</v>
       </c>
       <c r="E54" s="3">
-        <v>81300</v>
+        <v>73000</v>
       </c>
       <c r="F54" s="3">
-        <v>77000</v>
+        <v>77600</v>
       </c>
       <c r="G54" s="3">
-        <v>85100</v>
+        <v>78200</v>
       </c>
       <c r="H54" s="3">
-        <v>90800</v>
+        <v>79700</v>
       </c>
       <c r="I54" s="3">
-        <v>93000</v>
+        <v>85900</v>
       </c>
       <c r="J54" s="3">
+        <v>91700</v>
+      </c>
+      <c r="K54" s="3">
         <v>108600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>116100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>123000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>116700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,8 +2961,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2855,8 +2984,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2875,8 +3005,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2886,24 +3017,24 @@
       <c r="E57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3">
         <v>3600</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>8500</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,31 +3056,34 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="E58" s="3">
-        <v>50600</v>
+        <v>1500</v>
       </c>
       <c r="F58" s="3">
-        <v>2000</v>
+        <v>48300</v>
       </c>
       <c r="G58" s="3">
         <v>2100</v>
       </c>
       <c r="H58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J58" s="3">
         <v>2100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>17500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>2000</v>
       </c>
       <c r="K58" s="3">
         <v>2000</v>
@@ -2958,11 +3092,11 @@
         <v>2000</v>
       </c>
       <c r="M58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N58" s="3">
         <v>18600</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2975,44 +3109,47 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>24200</v>
+        <v>22800</v>
       </c>
       <c r="E59" s="3">
-        <v>22800</v>
+        <v>23300</v>
       </c>
       <c r="F59" s="3">
-        <v>20200</v>
+        <v>21800</v>
       </c>
       <c r="G59" s="3">
-        <v>28200</v>
+        <v>13900</v>
       </c>
       <c r="H59" s="3">
-        <v>27600</v>
+        <v>26500</v>
       </c>
       <c r="I59" s="3">
-        <v>12500</v>
+        <v>26200</v>
       </c>
       <c r="J59" s="3">
+        <v>27400</v>
+      </c>
+      <c r="K59" s="3">
         <v>27300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3025,44 +3162,47 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>25800</v>
+        <v>24100</v>
       </c>
       <c r="E60" s="3">
-        <v>73400</v>
+        <v>24900</v>
       </c>
       <c r="F60" s="3">
-        <v>25800</v>
+        <v>70100</v>
       </c>
       <c r="G60" s="3">
-        <v>30300</v>
+        <v>26200</v>
       </c>
       <c r="H60" s="3">
-        <v>29800</v>
+        <v>28400</v>
       </c>
       <c r="I60" s="3">
-        <v>29900</v>
+        <v>28200</v>
       </c>
       <c r="J60" s="3">
+        <v>29500</v>
+      </c>
+      <c r="K60" s="3">
         <v>37800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>36200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32800</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3075,44 +3215,47 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>45700</v>
+        <v>46000</v>
       </c>
       <c r="E61" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F61" s="3">
         <v>600</v>
       </c>
-      <c r="F61" s="3">
-        <v>44400</v>
-      </c>
       <c r="G61" s="3">
-        <v>44800</v>
+        <v>45000</v>
       </c>
       <c r="H61" s="3">
-        <v>48500</v>
+        <v>42000</v>
       </c>
       <c r="I61" s="3">
-        <v>49800</v>
+        <v>45900</v>
       </c>
       <c r="J61" s="3">
+        <v>49100</v>
+      </c>
+      <c r="K61" s="3">
         <v>50800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>51000</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3125,44 +3268,47 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1900</v>
+        <v>1300</v>
       </c>
       <c r="E62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1300</v>
       </c>
-      <c r="F62" s="3">
-        <v>1100</v>
-      </c>
       <c r="G62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H62" s="3">
+        <v>900</v>
+      </c>
+      <c r="I62" s="3">
+        <v>400</v>
+      </c>
+      <c r="J62" s="3">
+        <v>600</v>
+      </c>
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="H62" s="3">
-        <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>600</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
+        <v>900</v>
+      </c>
+      <c r="M62" s="3">
+        <v>700</v>
+      </c>
+      <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
-        <v>900</v>
-      </c>
-      <c r="L62" s="3">
-        <v>700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3321,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3225,8 +3374,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3275,8 +3427,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3325,44 +3480,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>73400</v>
+        <v>71400</v>
       </c>
       <c r="E66" s="3">
-        <v>75300</v>
+        <v>70700</v>
       </c>
       <c r="F66" s="3">
+        <v>71900</v>
+      </c>
+      <c r="G66" s="3">
+        <v>72400</v>
+      </c>
+      <c r="H66" s="3">
         <v>71300</v>
       </c>
-      <c r="G66" s="3">
-        <v>76100</v>
-      </c>
-      <c r="H66" s="3">
-        <v>78700</v>
-      </c>
       <c r="I66" s="3">
-        <v>80300</v>
+        <v>74400</v>
       </c>
       <c r="J66" s="3">
+        <v>79200</v>
+      </c>
+      <c r="K66" s="3">
         <v>89600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>93100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>84800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3375,8 +3533,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3395,8 +3556,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3445,8 +3607,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3495,8 +3660,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3536,8 +3704,8 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>3</v>
+      <c r="P70" s="3">
+        <v>0</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>3</v>
@@ -3545,8 +3713,11 @@
       <c r="R70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3595,31 +3766,34 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
+        <v>-177600</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -3636,8 +3810,8 @@
       <c r="O72" s="3">
         <v>0</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
+      <c r="P72" s="3">
+        <v>0</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
@@ -3645,8 +3819,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3695,8 +3872,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3745,8 +3925,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3795,44 +3978,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2400</v>
+        <v>-2700</v>
       </c>
       <c r="E76" s="3">
-        <v>6000</v>
+        <v>2300</v>
       </c>
       <c r="F76" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="G76" s="3">
-        <v>9000</v>
+        <v>5900</v>
       </c>
       <c r="H76" s="3">
-        <v>12100</v>
+        <v>8400</v>
       </c>
       <c r="I76" s="3">
-        <v>12600</v>
+        <v>11500</v>
       </c>
       <c r="J76" s="3">
+        <v>12500</v>
+      </c>
+      <c r="K76" s="3">
         <v>19000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>28800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>31900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3845,8 +4031,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3895,49 +4084,52 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3950,44 +4142,47 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
         <v>-9000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4195,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4020,44 +4218,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>1800</v>
       </c>
       <c r="E83" s="3">
-        <v>2000</v>
+        <v>1700</v>
       </c>
       <c r="F83" s="3">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="G83" s="3">
-        <v>1900</v>
+        <v>800</v>
       </c>
       <c r="H83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K83" s="3">
         <v>1800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1700</v>
       </c>
       <c r="L83" s="3">
         <v>1700</v>
       </c>
       <c r="M83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4269,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4120,8 +4322,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4170,8 +4375,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4220,8 +4428,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4270,8 +4481,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4320,44 +4534,47 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
-        <v>-1900</v>
-      </c>
       <c r="F89" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
-        <v>-2100</v>
-      </c>
       <c r="H89" s="3">
-        <v>-900</v>
+        <v>-2000</v>
       </c>
       <c r="I89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="K89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="L89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="M89" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="J89" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="K89" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="L89" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4370,8 +4587,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4390,49 +4610,50 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-2600</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-1200</v>
+        <v>-300</v>
       </c>
       <c r="F91" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>-6700</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-10800</v>
+        <v>-600</v>
       </c>
       <c r="I91" s="3">
-        <v>-800</v>
+        <v>-1000</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-12300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4500</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4440,8 +4661,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4490,8 +4714,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4540,44 +4767,47 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-100</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
       </c>
       <c r="G94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
-        <v>12300</v>
-      </c>
       <c r="I94" s="3">
-        <v>8100</v>
+        <v>11600</v>
       </c>
       <c r="J94" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K94" s="3">
         <v>6500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-21900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4590,8 +4820,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4610,31 +4843,32 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4660,8 +4894,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4710,8 +4947,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4760,8 +5000,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4810,34 +5053,37 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-4700</v>
+        <v>-600</v>
       </c>
       <c r="E100" s="3">
-        <v>4200</v>
+        <v>-4500</v>
       </c>
       <c r="F100" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-500</v>
       </c>
-      <c r="G100" s="3">
-        <v>-3800</v>
-      </c>
       <c r="H100" s="3">
-        <v>-1700</v>
+        <v>-3600</v>
       </c>
       <c r="I100" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="J100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-500</v>
       </c>
       <c r="L100" s="3">
         <v>-500</v>
@@ -4845,8 +5091,8 @@
       <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="N100" s="3">
+        <v>-500</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -4860,44 +5106,47 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="F101" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="G101" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="H101" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I101" s="3">
-        <v>-400</v>
+        <v>2300</v>
       </c>
       <c r="J101" s="3">
+        <v>700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4910,44 +5159,47 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-5700</v>
+        <v>-2400</v>
       </c>
       <c r="E102" s="3">
-        <v>2600</v>
+        <v>-5500</v>
       </c>
       <c r="F102" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1300</v>
       </c>
-      <c r="G102" s="3">
-        <v>-6500</v>
-      </c>
       <c r="H102" s="3">
-        <v>10600</v>
+        <v>-6100</v>
       </c>
       <c r="I102" s="3">
-        <v>1000</v>
+        <v>10100</v>
       </c>
       <c r="J102" s="3">
         <v>1000</v>
       </c>
       <c r="K102" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L102" s="3">
         <v>-11800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6400</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4958,6 +5210,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="92">
   <si>
     <t>ORXOY</t>
   </si>
@@ -656,89 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -763,35 +774,44 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>15300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>15500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>14300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="Q8" s="3">
         <v>15400</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -816,35 +836,44 @@
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
         <v>2500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>2700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>2100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>2700</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -869,35 +898,44 @@
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3">
         <v>12700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>12800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>12200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>12800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,8 +955,11 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -943,35 +984,44 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>8600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="O12" s="3">
         <v>7400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="P12" s="3">
         <v>7900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="Q12" s="3">
         <v>7000</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,8 +1073,17 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1049,14 +1108,14 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1067,17 +1126,26 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1102,14 +1170,14 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1120,17 +1188,26 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,8 +1224,11 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1173,35 +1253,44 @@
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3">
         <v>22200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>20300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>19100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="Q17" s="3">
         <v>16700</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1226,35 +1315,44 @@
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-7000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>-4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>-4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,8 +1372,11 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1300,35 +1401,44 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-2400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="O20" s="3">
         <v>2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1353,35 +1463,44 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-7600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="Q21" s="3">
         <v>100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1406,14 +1525,14 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1424,17 +1543,26 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1459,35 +1587,44 @@
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3">
         <v>-9400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>-3600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="Q23" s="3">
         <v>-1500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1512,35 +1649,44 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="P24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,8 +1738,17 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1618,35 +1773,44 @@
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3">
         <v>-9000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>-3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1671,35 +1835,44 @@
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3">
         <v>-9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>-3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1924,17 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1777,14 +1959,14 @@
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1795,17 +1977,26 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +2048,17 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,8 +2110,17 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1936,35 +2145,44 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>2400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="O32" s="3">
         <v>-2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="P32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1989,35 +2207,44 @@
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3">
         <v>-9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>-3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,8 +2296,17 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2095,93 +2331,111 @@
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3">
         <v>-9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>-3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2455,11 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,61 +2479,73 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11900</v>
+      </c>
+      <c r="F41" s="3">
+        <v>11100</v>
+      </c>
+      <c r="G41" s="3">
         <v>11300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>13200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
         <v>18500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>17000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>16900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>23300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>13800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>12900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>11800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>23600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>42400</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2299,26 +2568,26 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>13200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="N42" s="3">
         <v>21500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>31000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>21600</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,114 +2597,141 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F43" s="3">
+        <v>21100</v>
+      </c>
+      <c r="G43" s="3">
         <v>24200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>24300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>22800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>21200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>24700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>23200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>23700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>26700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>28500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>31900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>28800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F44" s="3">
         <v>5400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H44" s="3">
         <v>6500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>6700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>4200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>5900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>6200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>6200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>7300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>8600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>8200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>7500</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2448,8 +2744,8 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -2457,21 +2753,21 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>3600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2487,61 +2783,79 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>35400</v>
+      </c>
+      <c r="F46" s="3">
+        <v>40300</v>
+      </c>
+      <c r="G46" s="3">
         <v>40900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>44000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>48000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>45600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>47500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>52700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>56900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>72000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>79900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>85300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>78700</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2566,26 +2880,26 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>100</v>
-      </c>
-      <c r="M47" s="3">
-        <v>100</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>100</v>
+      </c>
+      <c r="P47" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>100</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2593,114 +2907,141 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G48" s="3">
         <v>8800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>9300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>9300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>10500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>10500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>10700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>10800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>12000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>11300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>11800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>11900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G49" s="3">
         <v>14100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>14600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
         <v>15500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="J49" s="3">
         <v>17200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>17100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>18300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>20000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>21300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>22200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>22800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>23400</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +3093,17 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,16 +3155,25 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>2200</v>
       </c>
       <c r="E52" s="3">
-        <v>100</v>
+        <v>2100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -2826,40 +3185,49 @@
         <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
       </c>
       <c r="K52" s="3">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>2700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>3000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="Q52" s="3">
         <v>2600</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,61 +3279,79 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>52700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>53700</v>
+      </c>
+      <c r="G54" s="3">
         <v>68700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>73000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>77600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>78200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>79700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>85900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>91700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>108600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>116100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>123000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>116700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3371,11 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,44 +3395,47 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="D57" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>8500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,28 +3451,37 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F58" s="3">
+        <v>900</v>
+      </c>
+      <c r="G58" s="3">
         <v>1300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="I58" s="3">
         <v>48300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2000</v>
       </c>
       <c r="J58" s="3">
         <v>2100</v>
@@ -3092,231 +3493,267 @@
         <v>2000</v>
       </c>
       <c r="M58" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N58" s="3">
         <v>2000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q58" s="3">
         <v>18600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>10600</v>
+      </c>
+      <c r="G59" s="3">
         <v>22800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>23300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>21800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>13900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>26500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>26200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>27400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>27300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>34200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>39700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>14200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>20500</v>
+      </c>
+      <c r="F60" s="3">
+        <v>20900</v>
+      </c>
+      <c r="G60" s="3">
         <v>24100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>24900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>70100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>26200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>28400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>28200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>29500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>37800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>36200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>41700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>32800</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>46300</v>
+      </c>
+      <c r="F61" s="3">
+        <v>42100</v>
+      </c>
+      <c r="G61" s="3">
         <v>46000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>44000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>45000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>42000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>45900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>49100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>50800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>50300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>50700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>51000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G62" s="3">
         <v>1300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>1800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>1300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>700</v>
       </c>
       <c r="N62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
+      <c r="O62" s="3">
+        <v>900</v>
+      </c>
+      <c r="P62" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>1000</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
@@ -3324,8 +3761,17 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3823,17 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3885,17 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,61 +3947,79 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>68800</v>
+      </c>
+      <c r="F66" s="3">
+        <v>65200</v>
+      </c>
+      <c r="G66" s="3">
         <v>71400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>70700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>71900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>72400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>71300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>74400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>79200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>89600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>87400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>93100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>84800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +4039,11 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +4095,17 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +4157,17 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3707,17 +4210,26 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,8 +4281,17 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3780,29 +4301,29 @@
       <c r="E72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="F72" s="3">
+        <v>-179700</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-177600</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3">
-        <v>0</v>
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N72" s="3">
         <v>0</v>
@@ -3813,17 +4334,26 @@
       <c r="P72" s="3">
         <v>0</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4405,17 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4467,17 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,61 +4529,79 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="F76" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="G76" s="3">
         <v>-2700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>2300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>5700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>5900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>8400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>11500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>12500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>19000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>28800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>29900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>31900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,66 +4653,84 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4171,35 +4755,44 @@
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3">
         <v>-9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>-3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,34 +4812,37 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="G83" s="3">
         <v>1800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>1700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>1800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>1600</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>1800</v>
       </c>
       <c r="L83" s="3">
         <v>1700</v>
@@ -4255,25 +4851,34 @@
         <v>1700</v>
       </c>
       <c r="N83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4930,17 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4992,17 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +5054,17 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +5116,17 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,61 +5178,79 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F89" s="3">
+        <v>600</v>
+      </c>
+      <c r="G89" s="3">
         <v>-1300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>-1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>-2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-5900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>-4800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-5900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-6000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,61 +5270,73 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3">
+        <v>100</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-12300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-1500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +5388,17 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,16 +5450,25 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-100</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>-300</v>
+        <v>-1900</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
@@ -4788,43 +5477,52 @@
         <v>-100</v>
       </c>
       <c r="H94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>11600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>8000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>6500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-6700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-21900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,8 +5542,11 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4870,14 +5571,14 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4897,8 +5598,17 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5660,17 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5722,17 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,163 +5784,199 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>-4500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="I100" s="3">
         <v>4000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>-500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
         <v>-3600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-500</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="H101" s="3">
         <v>900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F102" s="3">
+        <v>800</v>
+      </c>
+      <c r="G102" s="3">
         <v>-2400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>-5500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>2500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>-1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-6100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>10100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-11800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>-18700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-6400</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORXOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="92">
   <si>
     <t>ORXOY</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,8 +753,14 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -790,24 +797,24 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>15300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>15500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>14300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>15400</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -817,8 +824,14 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -855,23 +868,23 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>2500</v>
-      </c>
-      <c r="P9" s="3">
-        <v>2700</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>2100</v>
       </c>
       <c r="R9" s="3">
         <v>2700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
+      <c r="S9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T9" s="3">
+        <v>2700</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
@@ -882,8 +895,14 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -920,23 +939,23 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>12700</v>
-      </c>
-      <c r="P10" s="3">
-        <v>12800</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>12200</v>
       </c>
       <c r="R10" s="3">
         <v>12800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
+      <c r="S10" s="3">
+        <v>12200</v>
+      </c>
+      <c r="T10" s="3">
+        <v>12800</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
@@ -947,8 +966,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +997,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1010,24 +1037,24 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3">
         <v>8600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>7400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>7900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>7000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1064,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,8 +1135,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1140,11 +1179,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1158,17 +1197,23 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1205,11 +1250,11 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1223,17 +1268,23 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,8 +1305,10 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1292,24 +1345,24 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3">
         <v>22200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>20300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>19100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>16700</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1372,14 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1357,24 +1416,24 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-7000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1300</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1443,14 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,8 +1474,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1447,24 +1514,24 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-2400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,8 +1541,14 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1512,24 +1585,24 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-7600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1612,14 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1577,11 +1656,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1595,17 +1674,23 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1642,24 +1727,24 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-9400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1500</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,8 +1754,14 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1707,24 +1798,24 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1734,8 +1825,14 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,8 +1896,14 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1837,24 +1940,24 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-2300</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,8 +1967,14 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1902,24 +2011,24 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-9000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-2300</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +2038,14 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2109,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2032,11 +2153,11 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2050,17 +2171,23 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>3</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2251,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,8 +2322,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2227,24 +2366,24 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>2400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,8 +2393,14 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2292,24 +2437,24 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-9000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-2300</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2464,14 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,8 +2535,14 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2422,24 +2579,24 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-9000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-2300</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,67 +2606,73 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2682,14 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2713,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,62 +2740,64 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F41" s="3">
         <v>11200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>12800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>11100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>13200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>17000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>16900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>23300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>13800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>11800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>23600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>42400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,8 +2807,14 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2670,23 +2849,23 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>13200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>21500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>31000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>21600</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2699,62 +2878,68 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>25800</v>
+      </c>
+      <c r="F43" s="3">
         <v>18600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>19000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>17700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>21100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>24200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>24300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>22800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>21200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>24700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>23200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>23700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>26700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>28500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>31900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>28800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2764,62 +2949,68 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>4500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>4300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>3600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>6500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>6700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>4200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>6200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>6200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>7300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>8600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>8200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>7500</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2829,8 +3020,14 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2855,27 +3052,27 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>3600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,62 +3091,68 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>126400</v>
+      </c>
+      <c r="F46" s="3">
         <v>38600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>39000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>35400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>40300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>40900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>44000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>48000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>45600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>47500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>52700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>56900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>72000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>79900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>85300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>78700</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2959,8 +3162,14 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2997,11 +3206,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>100</v>
-      </c>
-      <c r="P47" s="3">
-        <v>100</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>100</v>
@@ -3009,11 +3218,11 @@
       <c r="R47" s="3">
         <v>100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>100</v>
+      </c>
+      <c r="T47" s="3">
+        <v>100</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -3024,62 +3233,68 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F48" s="3">
         <v>7500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>9300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>10500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>10500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>10700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>10800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>12000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>11300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>11800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>11900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,62 +3304,68 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>2500</v>
       </c>
       <c r="G49" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H49" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I49" s="3">
         <v>2400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>14100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>14600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>15500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>17200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>17100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>18300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>20000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>21300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>22200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>22800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>23400</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3154,8 +3375,14 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3446,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,25 +3517,31 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F52" s="3">
         <v>2200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>2200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>100</v>
@@ -3317,29 +3556,29 @@
         <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q52" s="3">
         <v>3200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>2600</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3588,14 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,62 +3659,68 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>141300</v>
+      </c>
+      <c r="F54" s="3">
         <v>55000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>56100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>52700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>53700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>68700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>73000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>77600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>78200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>79700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>85900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>91700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>108600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>116100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>123000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>116700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3730,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3761,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,53 +3788,55 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F57" s="3">
         <v>7200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
         <v>8500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,62 +3855,68 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>48300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>2000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>2100</v>
       </c>
       <c r="O58" s="3">
         <v>2000</v>
       </c>
       <c r="P58" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="Q58" s="3">
         <v>2000</v>
       </c>
       <c r="R58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T58" s="3">
         <v>18600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,62 +3926,68 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F59" s="3">
         <v>13700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>12500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>10500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>10600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>22800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>23300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>21800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>13900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>26500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>26200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>27400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>27300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>34200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>39700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>14200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,62 +3997,68 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F60" s="3">
         <v>27000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>26300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>20500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>20900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>24100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>24900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>70100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>26200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>28400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>28200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>29500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>37800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>36200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>41700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>32800</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3789,62 +4068,68 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>52500</v>
+      </c>
+      <c r="F61" s="3">
         <v>50400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>49900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>46300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>42100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>46000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>44000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>45000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>42000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>45900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>49100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>50800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>50300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>50700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>51000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3854,62 +4139,68 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F62" s="3">
         <v>1400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1800</v>
       </c>
       <c r="J62" s="3">
         <v>1300</v>
       </c>
       <c r="K62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="M62" s="3">
         <v>1200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3919,8 +4210,14 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4281,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4352,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,62 +4423,68 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>88100</v>
+      </c>
+      <c r="F66" s="3">
         <v>78800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>76800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>68800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>65200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>71400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>70700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>71900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>72400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>71300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>74400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>79200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>89600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>87400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>93100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>84800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4494,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4525,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4592,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4663,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4390,17 +4725,23 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-      <c r="U70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V70" s="3" t="s">
-        <v>3</v>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
       </c>
       <c r="W70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,49 +4805,55 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
+      <c r="E72" s="3">
+        <v>-147800</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>-179700</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>-177600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3">
-        <v>0</v>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q72" s="3">
         <v>0</v>
@@ -4520,17 +4867,23 @@
       <c r="T72" s="3">
         <v>0</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4947,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +5018,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,62 +5089,68 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>53200</v>
+      </c>
+      <c r="F76" s="3">
         <v>-23800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-20700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-16100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-11400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-2700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>12500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>19000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>28800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>29900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>31900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +5160,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,67 +5231,73 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,8 +5307,14 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4962,24 +5351,24 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-9000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-2300</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4989,8 +5378,14 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,62 +5409,64 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>2100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>2000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1700</v>
       </c>
       <c r="J83" s="3">
         <v>1800</v>
       </c>
       <c r="K83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>1700</v>
-      </c>
-      <c r="O83" s="3">
-        <v>1800</v>
       </c>
       <c r="P83" s="3">
         <v>1700</v>
       </c>
       <c r="Q83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R83" s="3">
         <v>1700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T83" s="3">
         <v>1500</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5079,8 +5476,14 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5547,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5618,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5689,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5760,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,62 +5831,68 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>87500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>600</v>
-      </c>
       <c r="H89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-4800</v>
       </c>
       <c r="P89" s="3">
         <v>-5900</v>
       </c>
       <c r="Q89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="R89" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="S89" s="3">
         <v>1400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-6000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5902,14 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,13 +5933,15 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>3</v>
@@ -5508,59 +5949,65 @@
       <c r="F91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G91" s="3">
-        <v>100</v>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-1000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-12300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-4500</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +6071,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,62 +6142,68 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-300</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
       </c>
       <c r="K94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>11600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>8000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>6500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-21900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5754,8 +6213,14 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6244,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5817,11 +6284,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5844,8 +6311,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6382,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6453,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,61 +6524,67 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-500</v>
+        <v>-51900</v>
       </c>
       <c r="E100" s="3">
         <v>500</v>
       </c>
       <c r="F100" s="3">
-        <v>-700</v>
+        <v>-500</v>
       </c>
       <c r="G100" s="3">
-        <v>-400</v>
+        <v>500</v>
       </c>
       <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>4000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-3600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-600</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-500</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-500</v>
       </c>
       <c r="R100" s="3">
         <v>-500</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
+      <c r="S100" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T100" s="3">
+        <v>-500</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
@@ -6104,62 +6595,68 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>2300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6169,62 +6666,68 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>87500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
       </c>
-      <c r="G102" s="3">
-        <v>800</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>10100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-18700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-6400</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6735,12 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
